--- a/downloads/en/structures-editoriales.xlsx
+++ b/downloads/en/structures-editoriales.xlsx
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         <v>40</v>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
